--- a/kanban_refs/04_Documentacao/maquinas.xlsx
+++ b/kanban_refs/04_Documentacao/maquinas.xlsx
@@ -8,19 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://metalogalva.sharepoint.com/sites/MetalogalvaIndicadores/Documentos Partilhados/09 Kanban Digital/04_Documentacao/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{9BD7D8DC-D0B8-42C8-AE6D-36688E1AFDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3C43282-BD5F-4FA1-B4DB-A96F80B07070}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{9BD7D8DC-D0B8-42C8-AE6D-36688E1AFDA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F4B5B63-FD16-47DA-AFDF-9851B66F377E}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5595" yWindow="4920" windowWidth="14400" windowHeight="8250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Export!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="311">
   <si>
     <t>codmaq</t>
   </si>
@@ -949,10 +965,10 @@
     <t>GUIFIL</t>
   </si>
   <si>
-    <t>MANUAL</t>
-  </si>
-  <si>
-    <t>LASER</t>
+    <t>QUINADORA ADIRA</t>
+  </si>
+  <si>
+    <t>QUINADORA PUMA</t>
   </si>
 </sst>
 </file>
@@ -972,12 +988,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -992,9 +1014,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1380,7 +1403,7 @@
       <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
@@ -1409,7 +1432,10 @@
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
@@ -1487,7 +1513,10 @@
       <c r="A6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
       </c>
       <c r="D6" t="s">
@@ -1565,7 +1594,7 @@
       <c r="A9" t="s">
         <v>51</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C9" t="s">
@@ -1597,9 +1626,6 @@
       <c r="B10" t="s">
         <v>58</v>
       </c>
-      <c r="C10" t="s">
-        <v>58</v>
-      </c>
       <c r="D10" t="s">
         <v>59</v>
       </c>
@@ -1623,7 +1649,7 @@
       <c r="A11" t="s">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C11" t="s">
@@ -1652,7 +1678,7 @@
       <c r="A12" t="s">
         <v>69</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C12" t="s">
@@ -1681,7 +1707,7 @@
       <c r="A13" t="s">
         <v>75</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C13" t="s">
@@ -1710,7 +1736,7 @@
       <c r="A14" t="s">
         <v>81</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
@@ -1739,7 +1765,7 @@
       <c r="A15" t="s">
         <v>87</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C15" t="s">
@@ -1768,7 +1794,7 @@
       <c r="A16" t="s">
         <v>93</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C16" t="s">
@@ -1797,8 +1823,11 @@
       <c r="A17" t="s">
         <v>99</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>100</v>
+      </c>
+      <c r="C17" t="s">
+        <v>309</v>
       </c>
       <c r="D17" t="s">
         <v>101</v>
@@ -1849,7 +1878,7 @@
       <c r="A19" t="s">
         <v>111</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C19" t="s">
@@ -1878,7 +1907,7 @@
       <c r="A20" t="s">
         <v>117</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>118</v>
       </c>
       <c r="C20" t="s">
@@ -1907,7 +1936,7 @@
       <c r="A21" t="s">
         <v>123</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C21" t="s">
@@ -1962,8 +1991,11 @@
       <c r="A23" t="s">
         <v>135</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>310</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -1988,11 +2020,11 @@
       <c r="A24" t="s">
         <v>141</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>142</v>
       </c>
       <c r="C24" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D24" t="s">
         <v>143</v>
@@ -2017,7 +2049,10 @@
       <c r="A25" t="s">
         <v>147</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" t="s">
         <v>148</v>
       </c>
       <c r="D25" t="s">
@@ -2043,11 +2078,11 @@
       <c r="A26" t="s">
         <v>153</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C26" t="s">
-        <v>309</v>
+        <v>154</v>
       </c>
       <c r="D26" t="s">
         <v>155</v>
@@ -2072,7 +2107,10 @@
       <c r="A27" t="s">
         <v>159</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" t="s">
         <v>160</v>
       </c>
       <c r="D27" t="s">
@@ -2124,7 +2162,10 @@
       <c r="A29" t="s">
         <v>171</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" t="s">
         <v>172</v>
       </c>
       <c r="D29" t="s">
@@ -2150,7 +2191,10 @@
       <c r="A30" t="s">
         <v>177</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" t="s">
         <v>178</v>
       </c>
       <c r="D30" t="s">
@@ -2176,7 +2220,7 @@
       <c r="A31" t="s">
         <v>183</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C31" t="s">
@@ -2205,11 +2249,11 @@
       <c r="A32" t="s">
         <v>189</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>310</v>
+        <v>190</v>
       </c>
       <c r="D32" t="s">
         <v>191</v>
@@ -2442,11 +2486,11 @@
       <c r="A41" t="s">
         <v>243</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="2" t="s">
         <v>244</v>
       </c>
       <c r="C41" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D41" t="s">
         <v>245</v>
@@ -2471,7 +2515,10 @@
       <c r="A42" t="s">
         <v>249</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" t="s">
         <v>250</v>
       </c>
       <c r="D42" t="s">
@@ -2523,7 +2570,10 @@
       <c r="A44" t="s">
         <v>261</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" t="s">
         <v>262</v>
       </c>
       <c r="D44" t="s">
@@ -2702,18 +2752,21 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0dd78b49-22a3-436a-be06-8c44c55b4835">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6c919bcf-8824-4a96-9763-fc1f714f2183" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2952,20 +3005,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="0dd78b49-22a3-436a-be06-8c44c55b4835">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6c919bcf-8824-4a96-9763-fc1f714f2183" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFFF9627-D3A0-4F38-8DCD-1077F3269F0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{210A4469-7DA8-4F47-BA18-6009F6839109}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0dd78b49-22a3-436a-be06-8c44c55b4835"/>
+    <ds:schemaRef ds:uri="6c919bcf-8824-4a96-9763-fc1f714f2183"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2990,12 +3044,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{210A4469-7DA8-4F47-BA18-6009F6839109}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFFF9627-D3A0-4F38-8DCD-1077F3269F0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0dd78b49-22a3-436a-be06-8c44c55b4835"/>
-    <ds:schemaRef ds:uri="6c919bcf-8824-4a96-9763-fc1f714f2183"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>